--- a/app/static/data_import/Book.xlsx
+++ b/app/static/data_import/Book.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/360e4cbd5b690b9a/Desktop/DoAnNganh/DoAnNganh/app/static/data_import/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="8_{9DE9052C-C128-4F62-8C12-DF5E9EDD52F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE40D3A0-5C59-4F3A-B638-7C16817518F7}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="8_{9DE9052C-C128-4F62-8C12-DF5E9EDD52F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A99F281D-50E8-4EF1-AE51-B376BE123AED}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{02DCAB5E-C2B4-41C2-AD3F-7AD0A3D5CF34}"/>
   </bookViews>
@@ -3757,10 +3757,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4081,11 +4077,11 @@
   <dimension ref="A1:F1001"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="77.6328125" customWidth="1"/>
-    <col min="2" max="2" width="25.6328125" customWidth="1"/>
-    <col min="3" max="3" width="19.90625" customWidth="1"/>
-    <col min="4" max="4" width="18.453125" customWidth="1"/>
-    <col min="5" max="5" width="16.90625" customWidth="1"/>
+    <col min="1" max="1" width="46.90625" customWidth="1"/>
+    <col min="2" max="2" width="14.6328125" customWidth="1"/>
+    <col min="3" max="3" width="18.6328125" customWidth="1"/>
+    <col min="4" max="4" width="16.26953125" customWidth="1"/>
+    <col min="5" max="5" width="12.6328125" customWidth="1"/>
     <col min="6" max="6" width="14.81640625" customWidth="1"/>
   </cols>
   <sheetData>
